--- a/src/database/email_sheet.xlsx
+++ b/src/database/email_sheet.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F89FD-BD5D-481C-A532-0CAF4E895D55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3056A35-0D3E-40DC-8D44-60D59AA01218}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FL" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FL!$E$1:$E$3815</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -36107,8 +36110,8 @@
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
     <col min="2" max="2" width="12.21875" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
